--- a/3-能力管理/运行记录类文件/JXTX-2025年1-11月运维服务能力改进计划及跟踪.xlsx
+++ b/3-能力管理/运行记录类文件/JXTX-2025年1-11月运维服务能力改进计划及跟踪.xlsx
@@ -4,13 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="120" windowWidth="22188" windowHeight="9575" activeTab="0"/>
+    <workbookView windowWidth="23040" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +29,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
   <si>
-    <t>2025年1-9月运维服务能力改进计划及跟踪</t>
+    <t>2025年1-11月运维服务能力改进计划及跟踪</t>
   </si>
   <si>
     <t>序号</t>
@@ -43,9 +42,6 @@
   </si>
   <si>
     <t>改进结果跟踪</t>
-  </si>
-  <si>
-    <t>备注</t>
   </si>
   <si>
     <t>待改进过程/活动</t>
@@ -87,22 +83,28 @@
 3.后期由管理人员不定期对此项工作进行抽查，杜绝同类事件的再次发生。</t>
   </si>
   <si>
+    <t>数智运营部</t>
+  </si>
+  <si>
+    <t>已完成</t>
+  </si>
+  <si>
+    <t>2025/1116</t>
+  </si>
+  <si>
     <t>张翔</t>
   </si>
   <si>
-    <t>已完成</t>
-  </si>
-  <si>
-    <t>配置管理考核指标</t>
+    <t>变更管理考核指标</t>
   </si>
   <si>
     <t>过程管理</t>
   </si>
   <si>
-    <t>未能满足配置管理考核指标</t>
-  </si>
-  <si>
-    <t>1.对相关运维人员进行培训，学习配置管理制度
+    <t>未能满足变更管理考核指标</t>
+  </si>
+  <si>
+    <t>1.对相关运维人员进行培训，学习变更管理制度
 2.后期质量管理人员对此进行抽查，杜绝此类事件再次发生</t>
   </si>
   <si>
@@ -121,13 +123,10 @@
     <t>满意度调查项中运维管理满意度较低</t>
   </si>
   <si>
-    <t>加强运维工程师专业技能培训，包括应急基础知识培训、专业知识技能培训</t>
+    <t>人力部对《满意度管理制度》和《沟通管理制度》进行宣贯</t>
   </si>
   <si>
     <t>质量管理部</t>
-  </si>
-  <si>
-    <t>数智运营部</t>
   </si>
 </sst>
 </file>
@@ -145,21 +144,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -167,25 +159,22 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u val="single"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u val="single"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -193,7 +182,6 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -202,7 +190,6 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -211,7 +198,6 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -220,7 +206,6 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -229,7 +214,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -238,7 +222,6 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -246,7 +229,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -255,7 +237,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -264,7 +245,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -273,7 +253,6 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -281,7 +260,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -290,7 +268,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -298,7 +275,6 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -306,7 +282,6 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -314,7 +289,6 @@
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -322,14 +296,18 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -527,6 +505,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -542,6 +535,7 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -550,6 +544,7 @@
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -558,6 +553,7 @@
       <bottom style="medium">
         <color theme="4" tint="0.49998"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -572,6 +568,7 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -586,6 +583,7 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -600,6 +598,7 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -608,6 +607,7 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -618,397 +618,153 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="93">
+  <cellStyleXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="31" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="31" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="57" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="57" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="79">
-    <cellStyle name="Normal" xfId="0"/>
-    <cellStyle name="Percent" xfId="15"/>
-    <cellStyle name="Currency" xfId="16"/>
-    <cellStyle name="Currency [0]" xfId="17"/>
-    <cellStyle name="Comma" xfId="18"/>
-    <cellStyle name="Comma [0]" xfId="19"/>
-    <cellStyle name="Percent" xfId="20"/>
-    <cellStyle name="Currency" xfId="21"/>
-    <cellStyle name="Currency [0]" xfId="22"/>
-    <cellStyle name="Comma" xfId="23"/>
-    <cellStyle name="Comma [0]" xfId="24"/>
-    <cellStyle name="Percent" xfId="25"/>
-    <cellStyle name="Currency" xfId="26"/>
-    <cellStyle name="Currency [0]" xfId="27"/>
-    <cellStyle name="Comma" xfId="28"/>
-    <cellStyle name="Comma [0]" xfId="29"/>
-    <cellStyle name="Percent" xfId="30"/>
-    <cellStyle name="Currency" xfId="31"/>
-    <cellStyle name="Currency [0]" xfId="32"/>
-    <cellStyle name="Comma" xfId="33"/>
-    <cellStyle name="Comma [0]" xfId="34"/>
-    <cellStyle name="Percent" xfId="35"/>
-    <cellStyle name="Currency" xfId="36"/>
-    <cellStyle name="Currency [0]" xfId="37"/>
-    <cellStyle name="Comma" xfId="38"/>
-    <cellStyle name="Comma [0]" xfId="39"/>
-    <cellStyle name="千位分隔" xfId="40"/>
-    <cellStyle name="货币" xfId="41"/>
-    <cellStyle name="百分比" xfId="42"/>
-    <cellStyle name="千位分隔[0]" xfId="43"/>
-    <cellStyle name="货币[0]" xfId="44"/>
-    <cellStyle name="超链接" xfId="45"/>
-    <cellStyle name="已访问的超链接" xfId="46"/>
-    <cellStyle name="注释" xfId="47"/>
-    <cellStyle name="警告文本" xfId="48"/>
-    <cellStyle name="标题" xfId="49"/>
-    <cellStyle name="解释性文本" xfId="50"/>
-    <cellStyle name="标题 1" xfId="51"/>
-    <cellStyle name="标题 2" xfId="52"/>
-    <cellStyle name="标题 3" xfId="53"/>
-    <cellStyle name="标题 4" xfId="54"/>
-    <cellStyle name="输入" xfId="55"/>
-    <cellStyle name="输出" xfId="56"/>
-    <cellStyle name="计算" xfId="57"/>
-    <cellStyle name="检查单元格" xfId="58"/>
-    <cellStyle name="链接单元格" xfId="59"/>
-    <cellStyle name="汇总" xfId="60"/>
-    <cellStyle name="好" xfId="61"/>
-    <cellStyle name="差" xfId="62"/>
-    <cellStyle name="适中" xfId="63"/>
-    <cellStyle name="强调文字颜色 1" xfId="64"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="65"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="66"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="67"/>
-    <cellStyle name="强调文字颜色 2" xfId="68"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="69"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="70"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="71"/>
-    <cellStyle name="强调文字颜色 3" xfId="72"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="73"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="74"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="75"/>
-    <cellStyle name="强调文字颜色 4" xfId="76"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="77"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="78"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="79"/>
-    <cellStyle name="强调文字颜色 5" xfId="80"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="81"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="82"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="83"/>
-    <cellStyle name="强调文字颜色 6" xfId="84"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="85"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="86"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="87"/>
-    <cellStyle name="Percent" xfId="88"/>
-    <cellStyle name="Currency" xfId="89"/>
-    <cellStyle name="Currency [0]" xfId="90"/>
-    <cellStyle name="Comma" xfId="91"/>
-    <cellStyle name="Comma [0]" xfId="92"/>
+  <cellStyles count="55">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="49"/>
+    <cellStyle name="Percent" xfId="50"/>
+    <cellStyle name="Currency" xfId="51"/>
+    <cellStyle name="Currency [0]" xfId="52"/>
+    <cellStyle name="Comma" xfId="53"/>
+    <cellStyle name="Comma [0]" xfId="54"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1303,22 +1059,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5"/>
+  <sheetPr/>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
   <cols>
-    <col min="2" max="2" width="20.875" customWidth="1"/>
-    <col min="3" max="3" width="10.875" customWidth="1"/>
-    <col min="4" max="4" width="17.875" customWidth="1"/>
-    <col min="5" max="5" width="26.625" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" customWidth="1"/>
+    <col min="3" max="3" width="10.8796296296296" customWidth="1"/>
+    <col min="4" max="4" width="17.8796296296296" customWidth="1"/>
+    <col min="5" max="5" width="26.6296296296296" customWidth="1"/>
     <col min="6" max="6" width="12.75" customWidth="1"/>
-    <col min="7" max="7" width="13.625" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="14.875" customWidth="1"/>
+    <col min="9" max="9" width="14.8796296296296" customWidth="1"/>
     <col min="10" max="10" width="9.75" customWidth="1"/>
-    <col min="11" max="11" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="41.25" customHeight="1">
+    <row r="1" ht="41.25" customHeight="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1331,9 +1087,8 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
     </row>
-    <row r="2" spans="1:11" ht="26.25" customHeight="1">
+    <row r="2" ht="26.25" customHeight="1" spans="1:10">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1352,148 +1107,141 @@
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
-      <c r="K2" s="3" t="s">
-        <v>5</v>
-      </c>
     </row>
-    <row r="3" spans="1:11" ht="26.25" customHeight="1">
+    <row r="3" ht="26.25" customHeight="1" spans="1:10">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" s="3"/>
     </row>
-    <row r="4" spans="1:11" ht="130" customHeight="1">
+    <row r="4" ht="130" customHeight="1" spans="1:10">
       <c r="A4" s="3">
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="G4" s="5">
-        <v>45916</v>
+        <v>45977</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="5">
-        <v>45916</v>
-      </c>
       <c r="J4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4" s="3"/>
+        <v>20</v>
+      </c>
     </row>
-    <row r="5" spans="1:11" ht="72">
+    <row r="5" ht="72" spans="1:10">
       <c r="A5" s="6">
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G5" s="9">
         <v>45992</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5" s="6"/>
+        <v>20</v>
+      </c>
     </row>
-    <row r="6" spans="1:11" ht="43.2">
+    <row r="6" ht="43.2" spans="1:10">
       <c r="A6" s="6">
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6" s="9">
         <v>45992</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K6" s="6"/>
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A1:K1"/>
+  <mergeCells count="5">
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="K2:K3"/>
   </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="87"/>
+  <pageSetup paperSize="9" scale="87" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/3-能力管理/运行记录类文件/JXTX-2025年1-11月运维服务能力改进计划及跟踪.xlsx
+++ b/3-能力管理/运行记录类文件/JXTX-2025年1-11月运维服务能力改进计划及跟踪.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView xWindow="240" yWindow="120" windowWidth="23040" windowHeight="9060" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames/>
+  <calcPr fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -144,14 +145,21 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -159,22 +167,25 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -182,6 +193,7 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -190,6 +202,7 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -198,6 +211,7 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -206,6 +220,7 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -214,6 +229,7 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -222,6 +238,7 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -229,6 +246,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -237,6 +255,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -245,6 +264,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -253,6 +273,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -260,6 +281,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -268,6 +290,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -275,6 +298,7 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -282,6 +306,7 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -289,6 +314,7 @@
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -296,18 +322,14 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -505,21 +527,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -535,7 +542,6 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -544,7 +550,6 @@
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -553,7 +558,6 @@
       <bottom style="medium">
         <color theme="4" tint="0.49998"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -568,7 +572,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -583,7 +586,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -598,7 +600,6 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -607,7 +608,6 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -618,153 +618,357 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="55">
+  <cellStyleXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="31" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="31" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="57" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="57" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="55">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="Normal" xfId="49"/>
-    <cellStyle name="Percent" xfId="50"/>
-    <cellStyle name="Currency" xfId="51"/>
-    <cellStyle name="Currency [0]" xfId="52"/>
-    <cellStyle name="Comma" xfId="53"/>
-    <cellStyle name="Comma [0]" xfId="54"/>
+  <cellStyles count="59">
+    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Percent" xfId="15"/>
+    <cellStyle name="Currency" xfId="16"/>
+    <cellStyle name="Currency [0]" xfId="17"/>
+    <cellStyle name="Comma" xfId="18"/>
+    <cellStyle name="Comma [0]" xfId="19"/>
+    <cellStyle name="千位分隔" xfId="20"/>
+    <cellStyle name="货币" xfId="21"/>
+    <cellStyle name="百分比" xfId="22"/>
+    <cellStyle name="千位分隔[0]" xfId="23"/>
+    <cellStyle name="货币[0]" xfId="24"/>
+    <cellStyle name="超链接" xfId="25"/>
+    <cellStyle name="已访问的超链接" xfId="26"/>
+    <cellStyle name="注释" xfId="27"/>
+    <cellStyle name="警告文本" xfId="28"/>
+    <cellStyle name="标题" xfId="29"/>
+    <cellStyle name="解释性文本" xfId="30"/>
+    <cellStyle name="标题 1" xfId="31"/>
+    <cellStyle name="标题 2" xfId="32"/>
+    <cellStyle name="标题 3" xfId="33"/>
+    <cellStyle name="标题 4" xfId="34"/>
+    <cellStyle name="输入" xfId="35"/>
+    <cellStyle name="输出" xfId="36"/>
+    <cellStyle name="计算" xfId="37"/>
+    <cellStyle name="检查单元格" xfId="38"/>
+    <cellStyle name="链接单元格" xfId="39"/>
+    <cellStyle name="汇总" xfId="40"/>
+    <cellStyle name="好" xfId="41"/>
+    <cellStyle name="差" xfId="42"/>
+    <cellStyle name="适中" xfId="43"/>
+    <cellStyle name="强调文字颜色 1" xfId="44"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="45"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="46"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="47"/>
+    <cellStyle name="强调文字颜色 2" xfId="48"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="49"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="50"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="51"/>
+    <cellStyle name="强调文字颜色 3" xfId="52"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="53"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="54"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="55"/>
+    <cellStyle name="强调文字颜色 4" xfId="56"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="57"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="58"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="59"/>
+    <cellStyle name="强调文字颜色 5" xfId="60"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="61"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="62"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="63"/>
+    <cellStyle name="强调文字颜色 6" xfId="64"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="65"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="66"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="67"/>
+    <cellStyle name="Percent" xfId="68"/>
+    <cellStyle name="Currency" xfId="69"/>
+    <cellStyle name="Currency [0]" xfId="70"/>
+    <cellStyle name="Comma" xfId="71"/>
+    <cellStyle name="Comma [0]" xfId="72"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1059,22 +1263,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5"/>
   <cols>
-    <col min="2" max="2" width="20.8796296296296" customWidth="1"/>
-    <col min="3" max="3" width="10.8796296296296" customWidth="1"/>
-    <col min="4" max="4" width="17.8796296296296" customWidth="1"/>
-    <col min="5" max="5" width="26.6296296296296" customWidth="1"/>
+    <col min="2" max="2" width="20.875" customWidth="1"/>
+    <col min="3" max="3" width="10.875" customWidth="1"/>
+    <col min="4" max="4" width="17.875" customWidth="1"/>
+    <col min="5" max="5" width="26.625" customWidth="1"/>
     <col min="6" max="6" width="12.75" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="14.8796296296296" customWidth="1"/>
+    <col min="9" max="9" width="14.875" customWidth="1"/>
     <col min="10" max="10" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="41.25" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="41.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1088,7 +1291,7 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
     </row>
-    <row r="2" ht="26.25" customHeight="1" spans="1:10">
+    <row r="2" spans="1:10" ht="26.25" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1108,7 +1311,7 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" ht="26.25" customHeight="1" spans="1:10">
+    <row r="3" spans="1:10" ht="26.25" customHeight="1">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3" t="s">
@@ -1136,7 +1339,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" ht="130" customHeight="1" spans="1:10">
+    <row r="4" spans="1:10" ht="130" customHeight="1">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -1168,7 +1371,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" ht="72" spans="1:10">
+    <row r="5" spans="1:10" ht="72">
       <c r="A5" s="6">
         <v>2</v>
       </c>
@@ -1200,7 +1403,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" ht="43.2" spans="1:10">
+    <row r="6" spans="1:10" ht="43.2">
       <c r="A6" s="6">
         <v>3</v>
       </c>
@@ -1241,7 +1444,6 @@
     <mergeCell ref="B2:B3"/>
   </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="87" orientation="landscape"/>
-  <headerFooter/>
+  <pageSetup orientation="landscape" paperSize="9" scale="87"/>
 </worksheet>
 </file>